--- a/실습폴더/학습준비물 빈 양식.xlsx
+++ b/실습폴더/학습준비물 빈 양식.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="학습준비물" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="학습준비물" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>아이스크림몰</t>
+          <t>쿠팡</t>
         </is>
       </c>
     </row>

--- a/실습폴더/학습준비물 빈 양식.xlsx
+++ b/실습폴더/학습준비물 빈 양식.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -469,210 +469,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A4 복사용지 500매</t>
+          <t>독도의날 만들기 키트</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80g</t>
+          <t>1인용</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>아이스크림몰</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>유성매직 12색 세트</t>
+          <t>한글날 만들기 키트</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1인용</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>아이스크림몰</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4절 도화지 100매</t>
+          <t>크리스마스 만들기 키트</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>180g</t>
+          <t>1인용</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>아이스크림몰</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>양면테이프 10m</t>
+          <t>물티슈</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12mm</t>
+          <t>캡형 70~100매, 10팩 묶음</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>아이스크림몰</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>가위 (안전가위)</t>
+          <t>각티슈</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>200매 이상, 6개 이상 묶음</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>딱풀 대용량</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>35g</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>56</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>색종이 양면 20매</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>전지 하드보드지 10매</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>학습용 화이트보드 개인용</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>28</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>보드마카 4색 세트</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>28</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>투명 L자 파일 10매</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>하이클레이 6색</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>28</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>쿠팡</t>
+          <t>아이스크림몰</t>
         </is>
       </c>
     </row>
